--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-05-21T22:07:00.506Z</t>
+    <t>2026-05-27T05:18:00.502Z</t>
   </si>
   <si>
     <t>AVG 2026 | FREE Antivirus, VPN &amp; TuneUp for All Your Devices</t>
